--- a/bizconfig/static-xlsx/moba/pixel_moba/hero_level_bonus.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/hero_level_bonus.xlsx
@@ -413,171 +413,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>hero_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>skill_point</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>exp_to_next</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>unlock_slot</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>max_mana</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>hp_regen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>mana_regen</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>physical_attack</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>magic_attack</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>physical_defense</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>magic_defense</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>attack_before</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>attack_after</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>attack_interval</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>attack_range</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>move_speed</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>collision_radius</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>vision_range</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>physical_lifesteal</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>magic_lifesteal</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>crit_rate</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>physical_pen</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>physical_pen_pct</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>magic_pen</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>magic_pen_pct</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>cd_reduction</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dodge</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>hit_rate</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>slow_resist</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>tenacity</t>
         </is>
@@ -591,160 +632,165 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>int32</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -753,7 +799,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>notnull</t>
+          <t>notnull&amp;only</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,14 +819,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>notnull</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>notnull</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>notnull</t>
@@ -912,6 +958,11 @@
         </is>
       </c>
       <c r="AG3" t="inlineStr">
+        <is>
+          <t>notnull</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>notnull</t>
         </is>
@@ -1083,236 +1134,245 @@
           <t>!s!c</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>!s!c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>复合主键:hero_id*1000+level,全表唯一(导出工具按 notnull&amp;only 校验)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>外键 -&gt; hero_profiles.hero_id</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>等级 1-10</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>升级时获得的技能点(通常 1,R解锁级可给 2)</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>升级时获得的技能点(通常 1,R 解锁级可给 2)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>升到下一级所需经验(level 10 留 0)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>本等级解锁内容(如 R 表示解锁大招),无则留空</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1级最大生命(该等级总值)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1级最大法力(该等级总值)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>每秒回血(该等级总值)</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>每秒回蓝(该等级总值)</t>
+          <t>生命回复/秒</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1级物理攻击(该等级总值)</t>
+          <t>法力回复/秒</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1级法术攻击(该等级总值)</t>
+          <t>物理攻击</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1级物理防御(该等级总值)</t>
+          <t>法术攻击</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1级法术防御(该等级总值)</t>
+          <t>物理防御</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>攻击前摇(秒)(该等级总值)</t>
+          <t>法术防御</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>攻击后摇(秒)(该等级总值)</t>
+          <t>攻击前摇</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>攻击间隔(秒)(该等级总值)</t>
+          <t>攻击后摇</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>攻击距离(像素)(该等级总值)</t>
+          <t>攻击间隔</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>移动速度(像素/秒)(该等级总值)</t>
+          <t>攻击距离</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>碰撞半径(像素)(该等级总值)</t>
+          <t>移动速度</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>视野范围(像素)(该等级总值)</t>
+          <t>碰撞半径</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>物理吸血(0-1)(该等级总值)</t>
+          <t>视野范围</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>法术吸血(0-1)(该等级总值)</t>
+          <t>物理吸血</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>暴击率(0-1)(该等级总值)</t>
+          <t>法术吸血</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>暴击伤害倍率(1.5=150%)(该等级总值)</t>
+          <t>暴击率</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>物理穿透(固定值)(该等级总值)</t>
+          <t>暴击伤害</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>物理穿透(0-1)(该等级总值)</t>
+          <t>物理穿透</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>法术穿透(固定值)(该等级总值)</t>
+          <t>物理穿透百分比</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>法术穿透(0-1)(该等级总值)</t>
+          <t>法术穿透</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>冷却缩减(0-0.4)(该等级总值)</t>
+          <t>法术穿透百分比</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>闪避率(0-1)(该等级总值)</t>
+          <t>冷却缩减</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>命中率(0-1)(该等级总值)</t>
+          <t>闪避率</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>减速抗性(0-1)(该等级总值)</t>
+          <t>命中率</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>韧性(减控0-1)(该等级总值)</t>
+          <t>减速抗性</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>韧性</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="B6" t="n">
         <v>1001</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>600</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>2.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1.5</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>55</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>20</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.3</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>0.4</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>40</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>220</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>400</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
@@ -1320,11 +1380,11 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
@@ -1341,77 +1401,79 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>1001002</v>
+      </c>
+      <c r="B7" t="n">
         <v>1001</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>150</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>680</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>320</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>62</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>22</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.3</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.4</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1.39</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>40</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>220</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>400</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
@@ -1419,11 +1481,11 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
@@ -1440,115 +1502,828 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1</v>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>1001003</v>
+      </c>
+      <c r="B8" t="n">
         <v>1001</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>262</v>
+      </c>
+      <c r="G8" t="n">
+        <v>772</v>
+      </c>
+      <c r="H8" t="n">
+        <v>345</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>69</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>24</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>40</v>
+      </c>
+      <c r="S8" t="n">
+        <v>221.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>405</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1001004</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>375</v>
+      </c>
+      <c r="G9" t="n">
+        <v>865</v>
+      </c>
+      <c r="H9" t="n">
+        <v>370</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>76</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>26</v>
+      </c>
+      <c r="N9" t="n">
+        <v>19</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R9" t="n">
+        <v>40</v>
+      </c>
+      <c r="S9" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>410</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1001005</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>488</v>
+      </c>
+      <c r="G10" t="n">
+        <v>958</v>
+      </c>
+      <c r="H10" t="n">
+        <v>395</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>28</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="R10" t="n">
+        <v>40</v>
+      </c>
+      <c r="S10" t="n">
+        <v>223.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>415</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1001006</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C11" t="n">
         <v>6</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E11" t="n">
         <v>600</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G11" t="n">
         <v>1050</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H11" t="n">
         <v>420</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I11" t="n">
         <v>3.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K11" t="n">
         <v>90</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>30</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N11" t="n">
         <v>22</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O11" t="n">
         <v>0.28</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P11" t="n">
         <v>0.38</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q11" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R11" t="n">
         <v>40</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S11" t="n">
         <v>225</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T11" t="n">
         <v>16</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U11" t="n">
         <v>420</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1</v>
       </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1001007</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>712</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1142</v>
+      </c>
+      <c r="H12" t="n">
+        <v>445</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>97</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>32</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="R12" t="n">
+        <v>40</v>
+      </c>
+      <c r="S12" t="n">
+        <v>226.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>16</v>
+      </c>
+      <c r="U12" t="n">
+        <v>425</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1001008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>825</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1235</v>
+      </c>
+      <c r="H13" t="n">
+        <v>470</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>104</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>34</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>40</v>
+      </c>
+      <c r="S13" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>16</v>
+      </c>
+      <c r="U13" t="n">
+        <v>430</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1001009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>938</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1328</v>
+      </c>
+      <c r="H14" t="n">
+        <v>495</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>111</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36</v>
+      </c>
+      <c r="N14" t="n">
+        <v>26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="R14" t="n">
+        <v>40</v>
+      </c>
+      <c r="S14" t="n">
+        <v>228.75</v>
+      </c>
+      <c r="T14" t="n">
+        <v>16</v>
+      </c>
+      <c r="U14" t="n">
+        <v>435</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1001010</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H15" t="n">
+        <v>520</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>118</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>40</v>
+      </c>
+      <c r="S15" t="n">
+        <v>230</v>
+      </c>
+      <c r="T15" t="n">
+        <v>16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>440</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0</v>
       </c>
     </row>
